--- a/modules/keydriver/docs/templates/KeyDriver_Config_Template.xlsx
+++ b/modules/keydriver/docs/templates/KeyDriver_Config_Template.xlsx
@@ -277,7 +277,7 @@
     <t xml:space="preserve">auto</t>
   </si>
   <si>
-    <t xml:space="preserve">Source of derived importance scores for quadrant placement</t>
+    <t xml:space="preserve">Source of derived importance scores for quadrant placement. 'auto' means the Shapley decomposition, which is also what the importance table is ranked by, so the quadrant and the table agree about which driver is biggest. It stays Shapley even when SHAP has run: set 'shap' explicitly to plot SHAP importance. Whichever source is asked for, the one actually used is written to the Run_Status sheet and to the interactive report.</t>
   </si>
   <si>
     <t xml:space="preserve">auto, shap, relative_weights, regression, or correlation</t>
